--- a/data/trans_dic/P1422-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1422-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,32</t>
+          <t>0,63; 3,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,27; 2,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,12</t>
+          <t>0,34; 2,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,18</t>
+          <t>0,14; 1,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,91</t>
+          <t>0,07; 0,7</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,55</t>
+          <t>0,84; 4,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,68</t>
+          <t>0,44; 2,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,96</t>
+          <t>0,19; 1,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,05</t>
+          <t>0,25; 2,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,69</t>
+          <t>0,23; 1,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,61</t>
+          <t>0,76; 2,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,22</t>
+          <t>0,22; 1,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,46</t>
+          <t>0,37; 1,45</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,43</t>
+          <t>0,29; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,08</t>
+          <t>0,24; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,71</t>
+          <t>1,61; 4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,26</t>
+          <t>0,5; 2,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,61</t>
+          <t>0,29; 1,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,31</t>
+          <t>0,13; 1,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,98</t>
+          <t>1,24; 2,96</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,31</t>
+          <t>0,24; 2,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,34</t>
+          <t>0,24; 2,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,56</t>
+          <t>0,26; 2,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,72</t>
+          <t>0,53; 3,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,72</t>
+          <t>0,52; 2,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,88</t>
+          <t>0,38; 1,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,21</t>
+          <t>0,41; 2,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,71</t>
+          <t>0,43; 1,84</t>
         </is>
       </c>
     </row>
@@ -1075,37 +1075,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1,95%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,15</t>
+          <t>0,47; 4,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,36</t>
+          <t>0,45; 4,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,08</t>
+          <t>0,63; 3,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,53</t>
+          <t>0,45; 4,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,11</t>
+          <t>0,55; 4,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,46</t>
+          <t>0,65; 2,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,31</t>
+          <t>0,73; 3,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,57</t>
+          <t>0,9; 4,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,77</t>
+          <t>0,87; 2,59</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,95</t>
+          <t>1,05; 3,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,21</t>
+          <t>0,8; 3,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,94</t>
+          <t>1,24; 3,05</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,92</t>
+          <t>0,47; 1,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,44</t>
+          <t>0,15; 1,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,69</t>
+          <t>0,18; 1,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,76</t>
+          <t>0,8; 2,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,97</t>
+          <t>0,15; 0,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,17</t>
+          <t>0,22; 1,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,52</t>
+          <t>0,77; 1,8</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,63</t>
+          <t>0,28; 1,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,37 +1458,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,9</t>
+          <t>0,77; 2,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,09</t>
+          <t>0,13; 1,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,52</t>
+          <t>0,13; 1,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,69</t>
+          <t>0,44; 1,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,11</t>
+          <t>0,27; 1,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,81</t>
+          <t>0,11; 0,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,54</t>
+          <t>0,71; 1,65</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,42</t>
+          <t>0,65; 1,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,94</t>
+          <t>0,41; 0,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,57</t>
+          <t>0,96; 1,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,06</t>
+          <t>0,46; 1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,9</t>
+          <t>0,35; 0,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,22</t>
+          <t>0,81; 1,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,09</t>
+          <t>0,64; 1,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,84</t>
+          <t>0,43; 0,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,31</t>
+          <t>0,94; 1,36</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>976</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1665</t>
         </is>
       </c>
     </row>
@@ -1861,22 +1861,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1003; 9795</t>
+          <t>1850; 10710</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6214</t>
+          <t>788; 7491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4149</t>
+          <t>0; 2843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5131</t>
+          <t>0; 5221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3691</t>
+          <t>0; 3664</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1984; 12326</t>
+          <t>1985; 11640</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>792; 6863</t>
+          <t>789; 7178</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>427; 5462</t>
+          <t>423; 4455</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7986</t>
         </is>
       </c>
     </row>
@@ -2024,22 +2024,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4285; 22993</t>
+          <t>4244; 21941</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2842; 13456</t>
+          <t>2187; 12417</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1290; 10089</t>
+          <t>1023; 10011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1124; 10752</t>
+          <t>1322; 10890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2049,22 +2049,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1245; 8683</t>
+          <t>1266; 8760</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7870; 26866</t>
+          <t>7786; 27359</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2225; 12505</t>
+          <t>2229; 12700</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3519; 15037</t>
+          <t>3967; 15559</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13279</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>936; 7885</t>
+          <t>930; 7719</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>774; 6614</t>
+          <t>777; 6572</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5263; 14896</t>
+          <t>5099; 15591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 8026</t>
+          <t>0; 7837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5036</t>
+          <t>0; 5055</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1786; 7899</t>
+          <t>1776; 8290</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1935; 10732</t>
+          <t>1925; 11150</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>989; 8567</t>
+          <t>869; 8618</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8386; 19851</t>
+          <t>8329; 19883</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7393</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>918; 8634</t>
+          <t>915; 7542</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>898; 8644</t>
+          <t>903; 8230</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8894</t>
+          <t>0; 11446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>995; 9950</t>
+          <t>1007; 10114</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2059; 14397</t>
+          <t>2041; 14518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1673; 8172</t>
+          <t>2173; 8842</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2929; 14371</t>
+          <t>2904; 12941</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3270; 16746</t>
+          <t>3119; 15701</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3107; 13511</t>
+          <t>3379; 14638</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6756</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1022; 8830</t>
+          <t>1008; 8564</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>945; 9204</t>
+          <t>946; 8447</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1293; 7292</t>
+          <t>1298; 7723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>999; 9944</t>
+          <t>988; 9706</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1201; 11174</t>
+          <t>1194; 10649</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1210; 5124</t>
+          <t>1471; 5910</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3015; 14289</t>
+          <t>3137; 14556</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3863; 15344</t>
+          <t>3849; 17523</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3634; 10727</t>
+          <t>3783; 11181</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10497</t>
         </is>
       </c>
     </row>
@@ -2676,22 +2676,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5972</t>
+          <t>0; 5359</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4118</t>
+          <t>0; 6115</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3173; 10652</t>
+          <t>2836; 10197</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7561</t>
+          <t>0; 6595</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2032; 8223</t>
+          <t>2100; 8372</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>962; 8451</t>
+          <t>951; 8430</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4865</t>
+          <t>0; 4769</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6441; 15467</t>
+          <t>6625; 16275</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>17992</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6579</t>
+          <t>0; 6616</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 9398</t>
+          <t>0; 11139</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2761; 11999</t>
+          <t>3380; 14153</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1095; 10020</t>
+          <t>1069; 10585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1119; 11648</t>
+          <t>1278; 11404</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3559; 14960</t>
+          <t>6143; 17117</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2110; 13093</t>
+          <t>2097; 12670</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3103; 15716</t>
+          <t>3016; 16860</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7927; 22324</t>
+          <t>11431; 26811</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>17931</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2244; 12712</t>
+          <t>2179; 13423</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,37 +3012,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3602; 17625</t>
+          <t>6133; 18965</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1061; 8975</t>
+          <t>1062; 8830</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1084; 12553</t>
+          <t>1085; 13083</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3074; 12061</t>
+          <t>3614; 13299</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5256; 17814</t>
+          <t>4387; 17515</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1085; 12972</t>
+          <t>1772; 13599</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8680; 25307</t>
+          <t>11530; 26829</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>23652; 48721</t>
+          <t>22359; 48363</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13945; 32006</t>
+          <t>13997; 32775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30356; 54428</t>
+          <t>33968; 57277</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16597; 37842</t>
+          <t>16530; 37599</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12769; 31761</t>
+          <t>12309; 33118</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25426; 44643</t>
+          <t>30323; 50455</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44325; 76054</t>
+          <t>44556; 75941</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>31121; 58608</t>
+          <t>29670; 58871</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60011; 93365</t>
+          <t>68425; 98810</t>
         </is>
       </c>
     </row>
